--- a/artfynd/A 29840-2026 artfynd.xlsx
+++ b/artfynd/A 29840-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128151269</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065276</t>
         </is>
       </c>
     </row>
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128151424</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130562329</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1224,6 +1249,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065267</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1339,6 +1369,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065271</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1450,6 +1485,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065274</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1561,6 +1601,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065268</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1672,6 +1717,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065275</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1778,6 +1828,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130562331</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1887,6 +1942,11 @@
       <c r="AY12" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065266</t>
         </is>
       </c>
     </row>
@@ -2019,6 +2079,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065270</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2125,6 +2190,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128151392</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2231,6 +2301,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128151409</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2342,6 +2417,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065273</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2458,6 +2538,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065331</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2574,6 +2659,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065335</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2685,6 +2775,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065347</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2791,6 +2886,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130562332</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2900,6 +3000,11 @@
       <c r="AY21" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065332</t>
         </is>
       </c>
     </row>
@@ -3008,6 +3113,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128151491</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3114,6 +3224,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130562327</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3220,6 +3335,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130562330</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3331,6 +3451,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065334</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3442,6 +3567,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065336</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3556,6 +3686,11 @@
       <c r="AY27" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065342</t>
         </is>
       </c>
     </row>
@@ -3664,6 +3799,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128151361</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3775,6 +3915,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065265</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3899,6 +4044,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065272</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4023,6 +4173,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065333</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4147,6 +4302,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065343</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4271,6 +4431,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065344</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4395,6 +4560,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065346</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4504,6 +4674,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128151453</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4627,6 +4802,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065260</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4754,6 +4934,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065261</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4863,6 +5048,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128151535</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4972,6 +5162,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128151618</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5086,6 +5281,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128151556</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5197,6 +5397,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065264</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5308,6 +5513,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065341</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5424,8 +5634,57 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065338</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29840-2026 artfynd.xlsx
+++ b/artfynd/A 29840-2026 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>135065276</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>135065267</v>
       </c>
       <c r="B6" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>135065271</v>
       </c>
       <c r="B7" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>135065274</v>
       </c>
       <c r="B8" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>135065268</v>
       </c>
       <c r="B9" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>135065275</v>
       </c>
       <c r="B10" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>135065266</v>
       </c>
       <c r="B12" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>135065270</v>
       </c>
       <c r="B13" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>135065273</v>
       </c>
       <c r="B16" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>135065331</v>
       </c>
       <c r="B17" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135065335</v>
       </c>
       <c r="B18" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>135065347</v>
       </c>
       <c r="B19" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>135065332</v>
       </c>
       <c r="B21" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>135065334</v>
       </c>
       <c r="B25" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>135065336</v>
       </c>
       <c r="B26" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>135065342</v>
       </c>
       <c r="B27" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>135065265</v>
       </c>
       <c r="B29" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>135065272</v>
       </c>
       <c r="B30" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>135065333</v>
       </c>
       <c r="B31" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>135065343</v>
       </c>
       <c r="B32" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>135065344</v>
       </c>
       <c r="B33" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>135065346</v>
       </c>
       <c r="B34" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>135065260</v>
       </c>
       <c r="B36" t="n">
-        <v>57153</v>
+        <v>57158</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>135065261</v>
       </c>
       <c r="B37" t="n">
-        <v>57153</v>
+        <v>57158</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>135065264</v>
       </c>
       <c r="B41" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>135065341</v>
       </c>
       <c r="B42" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>135065338</v>
       </c>
       <c r="B43" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 29840-2026 artfynd.xlsx
+++ b/artfynd/A 29840-2026 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>135065276</v>
       </c>
       <c r="B3" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>135065267</v>
       </c>
       <c r="B6" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>135065271</v>
       </c>
       <c r="B7" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>135065274</v>
       </c>
       <c r="B8" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>135065268</v>
       </c>
       <c r="B9" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>135065275</v>
       </c>
       <c r="B10" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>135065266</v>
       </c>
       <c r="B12" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>135065270</v>
       </c>
       <c r="B13" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>135065273</v>
       </c>
       <c r="B16" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>135065331</v>
       </c>
       <c r="B17" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135065335</v>
       </c>
       <c r="B18" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>135065347</v>
       </c>
       <c r="B19" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>135065332</v>
       </c>
       <c r="B21" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>135065334</v>
       </c>
       <c r="B25" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>135065336</v>
       </c>
       <c r="B26" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>135065342</v>
       </c>
       <c r="B27" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>135065265</v>
       </c>
       <c r="B29" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>135065264</v>
       </c>
       <c r="B41" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>135065341</v>
       </c>
       <c r="B42" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>135065338</v>
       </c>
       <c r="B43" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
